--- a/data/webinfo.xlsx
+++ b/data/webinfo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tannerfrank/Dropbox/Work/Devonian terr ecosystems/EcolNetworks/RhynieWebRepo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tannerfrank/Dropbox/Work/Devonian terr ecosystems/EcolNetworks/RhynieWebRepo/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA3CC81-A9CC-8E4B-AE38-A584A31AE76B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D6ACC0-A821-024D-AF73-38E668426832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="28800" windowHeight="16620" xr2:uid="{2FC7612B-5146-5244-858D-A0FBDE290E44}"/>
   </bookViews>
@@ -753,24 +753,6 @@
     <t>messel_terr_hi_cert</t>
   </si>
   <si>
-    <t>rhynie_complete</t>
-  </si>
-  <si>
-    <t>rhynie_aqu</t>
-  </si>
-  <si>
-    <t>rhynie_terr</t>
-  </si>
-  <si>
-    <t>rhynie_complete_lumped</t>
-  </si>
-  <si>
-    <t>rhynie_aqu_lumped</t>
-  </si>
-  <si>
-    <t>rhynie_terr_lumped</t>
-  </si>
-  <si>
     <t>web_derivation</t>
   </si>
   <si>
@@ -778,6 +760,24 @@
   </si>
   <si>
     <t>direct</t>
+  </si>
+  <si>
+    <t>rhynie_lumped_complete</t>
+  </si>
+  <si>
+    <t>rhynie_lumped_aqu</t>
+  </si>
+  <si>
+    <t>rhynie_unlumped_complete</t>
+  </si>
+  <si>
+    <t>rhynie_unlumped_aqu</t>
+  </si>
+  <si>
+    <t>rhynie_unlumped_terr</t>
+  </si>
+  <si>
+    <t>rhynie_lumped_terr</t>
   </si>
 </sst>
 </file>
@@ -827,10 +827,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -847,10 +846,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1194,7 +1189,7 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="E1" t="s">
         <v>5</v>
@@ -1244,7 +1239,7 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -1253,7 +1248,7 @@
         <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E2" t="s">
         <v>117</v>
@@ -1297,7 +1292,7 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -1306,7 +1301,7 @@
         <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -1347,7 +1342,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -1356,7 +1351,7 @@
         <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E4" t="s">
         <v>117</v>
@@ -1406,7 +1401,7 @@
         <v>115</v>
       </c>
       <c r="D5" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E5" t="s">
         <v>117</v>
@@ -1459,7 +1454,7 @@
         <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E6" t="s">
         <v>117</v>
@@ -1500,7 +1495,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
@@ -1509,7 +1504,7 @@
         <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E7" t="s">
         <v>117</v>
@@ -1559,7 +1554,7 @@
         <v>125</v>
       </c>
       <c r="D8" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E8" t="s">
         <v>116</v>
@@ -1618,7 +1613,7 @@
         <v>125</v>
       </c>
       <c r="D9" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E9" t="s">
         <v>116</v>
@@ -1674,7 +1669,7 @@
         <v>125</v>
       </c>
       <c r="D10" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E10" t="s">
         <v>116</v>
@@ -1730,7 +1725,7 @@
         <v>125</v>
       </c>
       <c r="D11" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E11" t="s">
         <v>116</v>
@@ -1789,7 +1784,7 @@
         <v>125</v>
       </c>
       <c r="D12" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E12" t="s">
         <v>116</v>
@@ -1845,7 +1840,7 @@
         <v>125</v>
       </c>
       <c r="D13" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E13" t="s">
         <v>116</v>
@@ -1901,7 +1896,7 @@
         <v>132</v>
       </c>
       <c r="D14" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="E14" t="s">
         <v>133</v>
@@ -1960,7 +1955,7 @@
         <v>136</v>
       </c>
       <c r="D15" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="E15" t="s">
         <v>133</v>
@@ -2016,7 +2011,7 @@
         <v>140</v>
       </c>
       <c r="D16" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="E16" t="s">
         <v>133</v>
@@ -2072,7 +2067,7 @@
         <v>140</v>
       </c>
       <c r="D17" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="E17" t="s">
         <v>133</v>
@@ -2124,16 +2119,16 @@
       <c r="B18" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s">
         <v>152</v>
       </c>
       <c r="D18" t="s">
-        <v>241</v>
-      </c>
-      <c r="E18" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E18" t="s">
         <v>133</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" t="s">
         <v>147</v>
       </c>
       <c r="G18" t="s">
@@ -2180,16 +2175,16 @@
       <c r="B19" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s">
         <v>153</v>
       </c>
       <c r="D19" t="s">
-        <v>241</v>
-      </c>
-      <c r="E19" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E19" t="s">
         <v>133</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" t="s">
         <v>147</v>
       </c>
       <c r="G19" t="s">
@@ -2236,13 +2231,13 @@
       <c r="B20" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s">
         <v>155</v>
       </c>
       <c r="D20" t="s">
-        <v>241</v>
-      </c>
-      <c r="E20" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E20" t="s">
         <v>133</v>
       </c>
       <c r="G20" t="s">
@@ -2292,13 +2287,13 @@
       <c r="B21" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s">
         <v>155</v>
       </c>
       <c r="D21" t="s">
-        <v>241</v>
-      </c>
-      <c r="E21" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E21" t="s">
         <v>133</v>
       </c>
       <c r="G21" t="s">
@@ -2348,13 +2343,13 @@
       <c r="B22" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" t="s">
         <v>157</v>
       </c>
       <c r="D22" t="s">
-        <v>241</v>
-      </c>
-      <c r="E22" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E22" t="s">
         <v>133</v>
       </c>
       <c r="G22" t="s">
@@ -2401,13 +2396,13 @@
       <c r="B23" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" t="s">
         <v>158</v>
       </c>
       <c r="D23" t="s">
-        <v>241</v>
-      </c>
-      <c r="E23" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E23" t="s">
         <v>133</v>
       </c>
       <c r="G23" t="s">
@@ -2454,13 +2449,13 @@
       <c r="B24" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" t="s">
         <v>162</v>
       </c>
       <c r="D24" t="s">
-        <v>241</v>
-      </c>
-      <c r="E24" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E24" t="s">
         <v>133</v>
       </c>
       <c r="F24" t="s">
@@ -2513,19 +2508,19 @@
       <c r="B25" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" t="s">
         <v>164</v>
       </c>
       <c r="D25" t="s">
-        <v>241</v>
-      </c>
-      <c r="E25" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E25" t="s">
         <v>133</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" t="s">
         <v>147</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" t="s">
         <v>156</v>
       </c>
       <c r="H25">
@@ -2572,19 +2567,19 @@
       <c r="B26" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" t="s">
         <v>169</v>
       </c>
       <c r="D26" t="s">
-        <v>241</v>
-      </c>
-      <c r="E26" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E26" t="s">
         <v>133</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" t="s">
         <v>134</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" t="s">
         <v>156</v>
       </c>
       <c r="H26">
@@ -2631,19 +2626,19 @@
       <c r="B27" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" t="s">
         <v>169</v>
       </c>
       <c r="D27" t="s">
-        <v>241</v>
-      </c>
-      <c r="E27" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E27" t="s">
         <v>133</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" t="s">
         <v>134</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" t="s">
         <v>156</v>
       </c>
       <c r="H27">
@@ -2690,19 +2685,19 @@
       <c r="B28" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" t="s">
         <v>169</v>
       </c>
       <c r="D28" t="s">
-        <v>241</v>
-      </c>
-      <c r="E28" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E28" t="s">
         <v>133</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" t="s">
         <v>134</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" t="s">
         <v>156</v>
       </c>
       <c r="H28">
@@ -2749,19 +2744,19 @@
       <c r="B29" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" t="s">
         <v>169</v>
       </c>
       <c r="D29" t="s">
-        <v>241</v>
-      </c>
-      <c r="E29" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E29" t="s">
         <v>133</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" t="s">
         <v>134</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" t="s">
         <v>156</v>
       </c>
       <c r="H29">
@@ -2808,19 +2803,19 @@
       <c r="B30" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" t="s">
         <v>170</v>
       </c>
       <c r="D30" t="s">
-        <v>241</v>
-      </c>
-      <c r="E30" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E30" t="s">
         <v>133</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" t="s">
         <v>147</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" t="s">
         <v>156</v>
       </c>
       <c r="H30">
@@ -2864,19 +2859,19 @@
       <c r="B31" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" t="s">
         <v>171</v>
       </c>
       <c r="D31" t="s">
-        <v>241</v>
-      </c>
-      <c r="E31" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E31" t="s">
         <v>133</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" t="s">
         <v>147</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" t="s">
         <v>119</v>
       </c>
       <c r="H31">
@@ -2920,16 +2915,16 @@
       <c r="B32" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" t="s">
         <v>173</v>
       </c>
       <c r="D32" t="s">
-        <v>241</v>
-      </c>
-      <c r="E32" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E32" t="s">
         <v>133</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" t="s">
         <v>156</v>
       </c>
       <c r="H32">
@@ -2973,19 +2968,19 @@
       <c r="B33" t="s">
         <v>48</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" t="s">
         <v>174</v>
       </c>
       <c r="D33" t="s">
-        <v>241</v>
-      </c>
-      <c r="E33" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E33" t="s">
         <v>133</v>
       </c>
       <c r="F33" t="s">
         <v>139</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" t="s">
         <v>156</v>
       </c>
       <c r="H33">
@@ -3036,15 +3031,15 @@
         <v>177</v>
       </c>
       <c r="D34" t="s">
-        <v>241</v>
-      </c>
-      <c r="E34" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E34" t="s">
         <v>133</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" t="s">
         <v>139</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" t="s">
         <v>119</v>
       </c>
       <c r="H34">
@@ -3085,16 +3080,16 @@
       <c r="B35" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" t="s">
         <v>178</v>
       </c>
       <c r="D35" t="s">
-        <v>241</v>
-      </c>
-      <c r="E35" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E35" t="s">
         <v>133</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" t="s">
         <v>156</v>
       </c>
       <c r="H35">
@@ -3135,13 +3130,13 @@
       <c r="B36" t="s">
         <v>48</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" t="s">
         <v>180</v>
       </c>
       <c r="D36" t="s">
-        <v>241</v>
-      </c>
-      <c r="E36" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E36" t="s">
         <v>133</v>
       </c>
       <c r="H36">
@@ -3185,19 +3180,19 @@
       <c r="B37" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" t="s">
         <v>171</v>
       </c>
       <c r="D37" t="s">
-        <v>241</v>
-      </c>
-      <c r="E37" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E37" t="s">
         <v>133</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" t="s">
         <v>147</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" t="s">
         <v>119</v>
       </c>
       <c r="H37">
@@ -3241,19 +3236,19 @@
       <c r="B38" t="s">
         <v>48</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" t="s">
         <v>181</v>
       </c>
       <c r="D38" t="s">
-        <v>241</v>
-      </c>
-      <c r="E38" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E38" t="s">
         <v>133</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" t="s">
         <v>147</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" t="s">
         <v>156</v>
       </c>
       <c r="H38">
@@ -3297,13 +3292,13 @@
       <c r="B39" t="s">
         <v>48</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" t="s">
         <v>183</v>
       </c>
       <c r="D39" t="s">
-        <v>241</v>
-      </c>
-      <c r="E39" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E39" t="s">
         <v>133</v>
       </c>
       <c r="H39">
@@ -3347,19 +3342,19 @@
       <c r="B40" t="s">
         <v>48</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" t="s">
         <v>185</v>
       </c>
       <c r="D40" t="s">
-        <v>241</v>
-      </c>
-      <c r="E40" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E40" t="s">
         <v>133</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" t="s">
         <v>134</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" t="s">
         <v>119</v>
       </c>
       <c r="H40">
@@ -3403,16 +3398,16 @@
       <c r="B41" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" t="s">
         <v>187</v>
       </c>
       <c r="D41" t="s">
-        <v>241</v>
-      </c>
-      <c r="E41" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E41" t="s">
         <v>133</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" t="s">
         <v>137</v>
       </c>
       <c r="H41">
@@ -3459,16 +3454,16 @@
       <c r="B42" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" t="s">
         <v>188</v>
       </c>
       <c r="D42" t="s">
-        <v>241</v>
-      </c>
-      <c r="E42" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E42" t="s">
         <v>133</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="G42" t="s">
         <v>137</v>
       </c>
       <c r="H42">
@@ -3515,16 +3510,16 @@
       <c r="B43" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" t="s">
         <v>189</v>
       </c>
       <c r="D43" t="s">
-        <v>241</v>
-      </c>
-      <c r="E43" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E43" t="s">
         <v>133</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G43" t="s">
         <v>137</v>
       </c>
       <c r="H43">
@@ -3571,16 +3566,16 @@
       <c r="B44" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" t="s">
         <v>190</v>
       </c>
       <c r="D44" t="s">
-        <v>241</v>
-      </c>
-      <c r="E44" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E44" t="s">
         <v>133</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" t="s">
         <v>137</v>
       </c>
       <c r="H44">
@@ -3627,19 +3622,19 @@
       <c r="B45" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" t="s">
         <v>191</v>
       </c>
       <c r="D45" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E45" t="s">
         <v>116</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" t="s">
         <v>147</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G45" t="s">
         <v>156</v>
       </c>
       <c r="H45">
@@ -3683,19 +3678,19 @@
       <c r="B46" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" t="s">
         <v>191</v>
       </c>
       <c r="D46" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E46" t="s">
         <v>116</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="F46" t="s">
         <v>147</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="G46" t="s">
         <v>156</v>
       </c>
       <c r="H46">
@@ -3739,19 +3734,19 @@
       <c r="B47" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" t="s">
         <v>191</v>
       </c>
       <c r="D47" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E47" t="s">
         <v>116</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F47" t="s">
         <v>147</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="G47" t="s">
         <v>156</v>
       </c>
       <c r="H47">
@@ -3795,19 +3790,19 @@
       <c r="B48" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" t="s">
         <v>191</v>
       </c>
       <c r="D48" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E48" t="s">
         <v>116</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="F48" t="s">
         <v>147</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="G48" t="s">
         <v>156</v>
       </c>
       <c r="H48">
@@ -3851,19 +3846,19 @@
       <c r="B49" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" t="s">
         <v>191</v>
       </c>
       <c r="D49" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E49" t="s">
         <v>116</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" t="s">
         <v>147</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="G49" t="s">
         <v>156</v>
       </c>
       <c r="H49">
@@ -3907,19 +3902,19 @@
       <c r="B50" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" t="s">
         <v>191</v>
       </c>
       <c r="D50" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E50" t="s">
         <v>116</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="F50" t="s">
         <v>147</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="G50" t="s">
         <v>156</v>
       </c>
       <c r="H50">
@@ -3963,19 +3958,19 @@
       <c r="B51" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" t="s">
         <v>191</v>
       </c>
       <c r="D51" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E51" t="s">
         <v>116</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F51" t="s">
         <v>147</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="G51" t="s">
         <v>156</v>
       </c>
       <c r="H51">
@@ -4019,19 +4014,19 @@
       <c r="B52" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" t="s">
         <v>191</v>
       </c>
       <c r="D52" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E52" t="s">
         <v>116</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F52" t="s">
         <v>147</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G52" t="s">
         <v>156</v>
       </c>
       <c r="H52">
@@ -4075,19 +4070,19 @@
       <c r="B53" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" t="s">
         <v>191</v>
       </c>
       <c r="D53" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E53" t="s">
         <v>116</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="F53" t="s">
         <v>147</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G53" t="s">
         <v>156</v>
       </c>
       <c r="H53">
@@ -4131,19 +4126,19 @@
       <c r="B54" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" t="s">
         <v>191</v>
       </c>
       <c r="D54" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E54" t="s">
         <v>116</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="F54" t="s">
         <v>147</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="G54" t="s">
         <v>156</v>
       </c>
       <c r="H54">
@@ -4187,19 +4182,19 @@
       <c r="B55" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" t="s">
         <v>191</v>
       </c>
       <c r="D55" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E55" t="s">
         <v>116</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F55" t="s">
         <v>147</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G55" t="s">
         <v>156</v>
       </c>
       <c r="H55">
@@ -4243,19 +4238,19 @@
       <c r="B56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" t="s">
         <v>191</v>
       </c>
       <c r="D56" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E56" t="s">
         <v>116</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="F56" t="s">
         <v>147</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="G56" t="s">
         <v>156</v>
       </c>
       <c r="H56">
@@ -4299,19 +4294,19 @@
       <c r="B57" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" t="s">
         <v>191</v>
       </c>
       <c r="D57" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E57" t="s">
         <v>116</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="F57" t="s">
         <v>147</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="G57" t="s">
         <v>156</v>
       </c>
       <c r="H57">
@@ -4355,19 +4350,19 @@
       <c r="B58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" t="s">
         <v>191</v>
       </c>
       <c r="D58" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E58" t="s">
         <v>116</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="F58" t="s">
         <v>147</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="G58" t="s">
         <v>156</v>
       </c>
       <c r="H58">
@@ -4411,19 +4406,19 @@
       <c r="B59" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" t="s">
         <v>191</v>
       </c>
       <c r="D59" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E59" t="s">
         <v>116</v>
       </c>
-      <c r="F59" s="2" t="s">
+      <c r="F59" t="s">
         <v>147</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="G59" t="s">
         <v>156</v>
       </c>
       <c r="H59">
@@ -4467,19 +4462,19 @@
       <c r="B60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" t="s">
         <v>191</v>
       </c>
       <c r="D60" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E60" t="s">
         <v>116</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="F60" t="s">
         <v>147</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="G60" t="s">
         <v>156</v>
       </c>
       <c r="H60">
@@ -4523,19 +4518,19 @@
       <c r="B61" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" t="s">
         <v>191</v>
       </c>
       <c r="D61" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E61" t="s">
         <v>116</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="F61" t="s">
         <v>147</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" t="s">
         <v>156</v>
       </c>
       <c r="H61">
@@ -4579,19 +4574,19 @@
       <c r="B62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" t="s">
         <v>191</v>
       </c>
       <c r="D62" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E62" t="s">
         <v>116</v>
       </c>
-      <c r="F62" s="2" t="s">
+      <c r="F62" t="s">
         <v>147</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="G62" t="s">
         <v>156</v>
       </c>
       <c r="H62">
@@ -4635,19 +4630,19 @@
       <c r="B63" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" t="s">
         <v>191</v>
       </c>
       <c r="D63" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E63" t="s">
         <v>116</v>
       </c>
-      <c r="F63" s="2" t="s">
+      <c r="F63" t="s">
         <v>147</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="G63" t="s">
         <v>156</v>
       </c>
       <c r="H63">
@@ -4691,19 +4686,19 @@
       <c r="B64" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" t="s">
         <v>191</v>
       </c>
       <c r="D64" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E64" t="s">
         <v>116</v>
       </c>
-      <c r="F64" s="2" t="s">
+      <c r="F64" t="s">
         <v>147</v>
       </c>
-      <c r="G64" s="2" t="s">
+      <c r="G64" t="s">
         <v>156</v>
       </c>
       <c r="H64">
@@ -4747,19 +4742,19 @@
       <c r="B65" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" t="s">
         <v>191</v>
       </c>
       <c r="D65" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E65" t="s">
         <v>116</v>
       </c>
-      <c r="F65" s="2" t="s">
+      <c r="F65" t="s">
         <v>147</v>
       </c>
-      <c r="G65" s="2" t="s">
+      <c r="G65" t="s">
         <v>156</v>
       </c>
       <c r="H65">
@@ -4803,19 +4798,19 @@
       <c r="B66" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" t="s">
         <v>191</v>
       </c>
       <c r="D66" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E66" t="s">
         <v>116</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="F66" t="s">
         <v>147</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="G66" t="s">
         <v>156</v>
       </c>
       <c r="H66">
@@ -4859,19 +4854,19 @@
       <c r="B67" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" t="s">
         <v>191</v>
       </c>
       <c r="D67" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E67" t="s">
         <v>116</v>
       </c>
-      <c r="F67" s="2" t="s">
+      <c r="F67" t="s">
         <v>147</v>
       </c>
-      <c r="G67" s="2" t="s">
+      <c r="G67" t="s">
         <v>156</v>
       </c>
       <c r="H67">
@@ -4915,19 +4910,19 @@
       <c r="B68" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" t="s">
         <v>191</v>
       </c>
       <c r="D68" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E68" t="s">
         <v>116</v>
       </c>
-      <c r="F68" s="2" t="s">
+      <c r="F68" t="s">
         <v>147</v>
       </c>
-      <c r="G68" s="2" t="s">
+      <c r="G68" t="s">
         <v>156</v>
       </c>
       <c r="H68">
@@ -4971,19 +4966,19 @@
       <c r="B69" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" t="s">
         <v>191</v>
       </c>
       <c r="D69" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E69" t="s">
         <v>116</v>
       </c>
-      <c r="F69" s="2" t="s">
+      <c r="F69" t="s">
         <v>147</v>
       </c>
-      <c r="G69" s="2" t="s">
+      <c r="G69" t="s">
         <v>156</v>
       </c>
       <c r="H69">
@@ -5027,19 +5022,19 @@
       <c r="B70" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" t="s">
         <v>191</v>
       </c>
       <c r="D70" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E70" t="s">
         <v>116</v>
       </c>
-      <c r="F70" s="2" t="s">
+      <c r="F70" t="s">
         <v>147</v>
       </c>
-      <c r="G70" s="2" t="s">
+      <c r="G70" t="s">
         <v>156</v>
       </c>
       <c r="H70">
@@ -5083,19 +5078,19 @@
       <c r="B71" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" t="s">
         <v>191</v>
       </c>
       <c r="D71" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E71" t="s">
         <v>116</v>
       </c>
-      <c r="F71" s="2" t="s">
+      <c r="F71" t="s">
         <v>147</v>
       </c>
-      <c r="G71" s="2" t="s">
+      <c r="G71" t="s">
         <v>156</v>
       </c>
       <c r="H71">
@@ -5139,19 +5134,19 @@
       <c r="B72" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" t="s">
         <v>191</v>
       </c>
       <c r="D72" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E72" t="s">
         <v>116</v>
       </c>
-      <c r="F72" s="2" t="s">
+      <c r="F72" t="s">
         <v>147</v>
       </c>
-      <c r="G72" s="2" t="s">
+      <c r="G72" t="s">
         <v>156</v>
       </c>
       <c r="H72">
@@ -5195,19 +5190,19 @@
       <c r="B73" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" t="s">
         <v>191</v>
       </c>
       <c r="D73" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E73" t="s">
         <v>116</v>
       </c>
-      <c r="F73" s="2" t="s">
+      <c r="F73" t="s">
         <v>147</v>
       </c>
-      <c r="G73" s="2" t="s">
+      <c r="G73" t="s">
         <v>156</v>
       </c>
       <c r="H73">
@@ -5251,19 +5246,19 @@
       <c r="B74" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" t="s">
         <v>191</v>
       </c>
       <c r="D74" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E74" t="s">
         <v>116</v>
       </c>
-      <c r="F74" s="2" t="s">
+      <c r="F74" t="s">
         <v>147</v>
       </c>
-      <c r="G74" s="2" t="s">
+      <c r="G74" t="s">
         <v>156</v>
       </c>
       <c r="H74">
@@ -5307,19 +5302,19 @@
       <c r="B75" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" t="s">
         <v>191</v>
       </c>
       <c r="D75" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E75" t="s">
         <v>116</v>
       </c>
-      <c r="F75" s="2" t="s">
+      <c r="F75" t="s">
         <v>147</v>
       </c>
-      <c r="G75" s="2" t="s">
+      <c r="G75" t="s">
         <v>156</v>
       </c>
       <c r="H75">
@@ -5363,19 +5358,19 @@
       <c r="B76" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" t="s">
         <v>191</v>
       </c>
       <c r="D76" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E76" t="s">
         <v>116</v>
       </c>
-      <c r="F76" s="2" t="s">
+      <c r="F76" t="s">
         <v>147</v>
       </c>
-      <c r="G76" s="2" t="s">
+      <c r="G76" t="s">
         <v>156</v>
       </c>
       <c r="H76">
@@ -5419,19 +5414,19 @@
       <c r="B77" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" t="s">
         <v>191</v>
       </c>
       <c r="D77" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E77" t="s">
         <v>116</v>
       </c>
-      <c r="F77" s="2" t="s">
+      <c r="F77" t="s">
         <v>147</v>
       </c>
-      <c r="G77" s="2" t="s">
+      <c r="G77" t="s">
         <v>156</v>
       </c>
       <c r="H77">
@@ -5475,19 +5470,19 @@
       <c r="B78" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" t="s">
         <v>191</v>
       </c>
       <c r="D78" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E78" t="s">
         <v>116</v>
       </c>
-      <c r="F78" s="2" t="s">
+      <c r="F78" t="s">
         <v>147</v>
       </c>
-      <c r="G78" s="2" t="s">
+      <c r="G78" t="s">
         <v>156</v>
       </c>
       <c r="H78">
@@ -5531,19 +5526,19 @@
       <c r="B79" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" t="s">
         <v>191</v>
       </c>
       <c r="D79" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E79" t="s">
         <v>116</v>
       </c>
-      <c r="F79" s="2" t="s">
+      <c r="F79" t="s">
         <v>147</v>
       </c>
-      <c r="G79" s="2" t="s">
+      <c r="G79" t="s">
         <v>156</v>
       </c>
       <c r="H79">
@@ -5587,19 +5582,19 @@
       <c r="B80" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" t="s">
         <v>191</v>
       </c>
       <c r="D80" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E80" t="s">
         <v>116</v>
       </c>
-      <c r="F80" s="2" t="s">
+      <c r="F80" t="s">
         <v>147</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="G80" t="s">
         <v>156</v>
       </c>
       <c r="H80">
@@ -5643,19 +5638,19 @@
       <c r="B81" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" t="s">
         <v>191</v>
       </c>
       <c r="D81" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E81" t="s">
         <v>116</v>
       </c>
-      <c r="F81" s="2" t="s">
+      <c r="F81" t="s">
         <v>147</v>
       </c>
-      <c r="G81" s="2" t="s">
+      <c r="G81" t="s">
         <v>156</v>
       </c>
       <c r="H81">
@@ -5699,19 +5694,19 @@
       <c r="B82" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" t="s">
         <v>191</v>
       </c>
       <c r="D82" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E82" t="s">
         <v>116</v>
       </c>
-      <c r="F82" s="2" t="s">
+      <c r="F82" t="s">
         <v>147</v>
       </c>
-      <c r="G82" s="2" t="s">
+      <c r="G82" t="s">
         <v>156</v>
       </c>
       <c r="H82">
@@ -5755,19 +5750,19 @@
       <c r="B83" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" t="s">
         <v>191</v>
       </c>
       <c r="D83" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E83" t="s">
         <v>116</v>
       </c>
-      <c r="F83" s="2" t="s">
+      <c r="F83" t="s">
         <v>147</v>
       </c>
-      <c r="G83" s="2" t="s">
+      <c r="G83" t="s">
         <v>156</v>
       </c>
       <c r="H83">
@@ -5811,19 +5806,19 @@
       <c r="B84" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" t="s">
         <v>191</v>
       </c>
       <c r="D84" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E84" t="s">
         <v>116</v>
       </c>
-      <c r="F84" s="2" t="s">
+      <c r="F84" t="s">
         <v>147</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="G84" t="s">
         <v>156</v>
       </c>
       <c r="H84">
@@ -5867,19 +5862,19 @@
       <c r="B85" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" t="s">
         <v>191</v>
       </c>
       <c r="D85" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E85" t="s">
         <v>116</v>
       </c>
-      <c r="F85" s="2" t="s">
+      <c r="F85" t="s">
         <v>147</v>
       </c>
-      <c r="G85" s="2" t="s">
+      <c r="G85" t="s">
         <v>156</v>
       </c>
       <c r="H85">
@@ -5923,19 +5918,19 @@
       <c r="B86" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" t="s">
         <v>191</v>
       </c>
       <c r="D86" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E86" t="s">
         <v>116</v>
       </c>
-      <c r="F86" s="2" t="s">
+      <c r="F86" t="s">
         <v>147</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="G86" t="s">
         <v>156</v>
       </c>
       <c r="H86">
@@ -5979,19 +5974,19 @@
       <c r="B87" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" t="s">
         <v>191</v>
       </c>
       <c r="D87" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E87" t="s">
         <v>116</v>
       </c>
-      <c r="F87" s="2" t="s">
+      <c r="F87" t="s">
         <v>147</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="G87" t="s">
         <v>156</v>
       </c>
       <c r="H87">
@@ -6035,19 +6030,19 @@
       <c r="B88" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" t="s">
         <v>191</v>
       </c>
       <c r="D88" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E88" t="s">
         <v>116</v>
       </c>
-      <c r="F88" s="2" t="s">
+      <c r="F88" t="s">
         <v>147</v>
       </c>
-      <c r="G88" s="2" t="s">
+      <c r="G88" t="s">
         <v>156</v>
       </c>
       <c r="H88">
@@ -6091,19 +6086,19 @@
       <c r="B89" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" t="s">
         <v>191</v>
       </c>
       <c r="D89" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E89" t="s">
         <v>116</v>
       </c>
-      <c r="F89" s="2" t="s">
+      <c r="F89" t="s">
         <v>147</v>
       </c>
-      <c r="G89" s="2" t="s">
+      <c r="G89" t="s">
         <v>156</v>
       </c>
       <c r="H89">
@@ -6147,19 +6142,19 @@
       <c r="B90" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" t="s">
         <v>191</v>
       </c>
       <c r="D90" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E90" t="s">
         <v>116</v>
       </c>
-      <c r="F90" s="2" t="s">
+      <c r="F90" t="s">
         <v>147</v>
       </c>
-      <c r="G90" s="2" t="s">
+      <c r="G90" t="s">
         <v>156</v>
       </c>
       <c r="H90">
@@ -6203,19 +6198,19 @@
       <c r="B91" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" t="s">
         <v>191</v>
       </c>
       <c r="D91" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E91" t="s">
         <v>116</v>
       </c>
-      <c r="F91" s="2" t="s">
+      <c r="F91" t="s">
         <v>147</v>
       </c>
-      <c r="G91" s="2" t="s">
+      <c r="G91" t="s">
         <v>156</v>
       </c>
       <c r="H91">
@@ -6259,19 +6254,19 @@
       <c r="B92" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" t="s">
         <v>191</v>
       </c>
       <c r="D92" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E92" t="s">
         <v>116</v>
       </c>
-      <c r="F92" s="2" t="s">
+      <c r="F92" t="s">
         <v>147</v>
       </c>
-      <c r="G92" s="2" t="s">
+      <c r="G92" t="s">
         <v>156</v>
       </c>
       <c r="H92">
@@ -6456,16 +6451,16 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>198</v>
       </c>
     </row>
